--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92564430331</v>
+        <v>46157.93085005254</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93085005254</v>
+        <v>46157.93163111746</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93163111746</v>
+        <v>46157.93396541017</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93396541017</v>
+        <v>46157.93713915146</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93713915146</v>
+        <v>46158.28212967641</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28212967641</v>
+        <v>46158.29674180999</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29674180999</v>
+        <v>46158.29810562615</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29810562615</v>
+        <v>46158.33383855149</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33383855149</v>
+        <v>46158.36852425931</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36852425931</v>
+        <v>46158.37284000622</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
